--- a/backend/data/location/钻孔位置.xlsx
+++ b/backend/data/location/钻孔位置.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\资料清单\【01】钻孔柱状图\整理数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GeoMine3D\backend\data\location\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD5DA6E-8FF7-451D-A6FE-C54C5441DC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F608D927-7FAB-49BE-A03F-D69F3A8D7D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5184" yWindow="2160" windowWidth="23040" windowHeight="13464" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4236" yWindow="2148" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/backend/data/location/钻孔位置.xlsx
+++ b/backend/data/location/钻孔位置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GeoMine3D\backend\data\location\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F608D927-7FAB-49BE-A03F-D69F3A8D7D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADCFDF8-A72F-4B7F-8AEA-0828CD6BAD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4236" yWindow="2148" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3852" yWindow="3072" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>213</v>

--- a/backend/data/location/钻孔位置.xlsx
+++ b/backend/data/location/钻孔位置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GeoMine3D\backend\data\location\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADCFDF8-A72F-4B7F-8AEA-0828CD6BAD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2567DA-8D67-4E56-96D0-D31147C74780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3852" yWindow="3072" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="2004" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>213</v>
